--- a/data/trans_bre/P23_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 0,55</t>
+          <t>-12,18; 0,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 4,6</t>
+          <t>-9,23; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -1,72</t>
+          <t>-14,22; -1,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 1,4</t>
+          <t>-26,74; 1,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 13,33</t>
+          <t>-22,45; 11,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,99; -5,72</t>
+          <t>-37,06; -5,03</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -11,77</t>
+          <t>-22,3; -11,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,73; -4,66</t>
+          <t>-15,38; -4,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -1,39</t>
+          <t>-13,35; -2,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,09; -22,4</t>
+          <t>-39,07; -21,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -9,86</t>
+          <t>-28,64; -9,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,59; -3,18</t>
+          <t>-27,53; -4,76</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -9,72</t>
+          <t>-21,36; -10,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,36; -7,56</t>
+          <t>-18,21; -6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -1,58</t>
+          <t>-12,26; -1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,13; -19,54</t>
+          <t>-38,71; -20,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,56; -16,85</t>
+          <t>-36,51; -15,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,59; -4,07</t>
+          <t>-28,2; -3,49</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -10,42</t>
+          <t>-23,07; -10,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -0,0</t>
+          <t>-12,21; -0,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -1,77</t>
+          <t>-12,92; -1,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,96; -24,6</t>
+          <t>-47,62; -25,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 0,04</t>
+          <t>-25,34; -1,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,31; -4,39</t>
+          <t>-28,46; -3,47</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,33; -15,69</t>
+          <t>-27,09; -15,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -15,24</t>
+          <t>-26,73; -15,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -1,45</t>
+          <t>-13,22; -1,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-74,02; -51,7</t>
+          <t>-74,38; -52,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,23; -46,48</t>
+          <t>-68,21; -45,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -4,9</t>
+          <t>-39,71; -6,92</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -12,07</t>
+          <t>-21,18; -11,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -5,84</t>
+          <t>-16,54; -6,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -4,21</t>
+          <t>-14,69; -4,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-95,6; -78,05</t>
+          <t>-95,75; -77,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -42,98</t>
+          <t>-82,89; -44,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -29,22</t>
+          <t>-71,01; -30,84</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -5,15</t>
+          <t>-14,22; -5,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -5,77</t>
+          <t>-14,34; -5,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -4,0</t>
+          <t>-11,68; -4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-96,55; -63,57</t>
+          <t>-97,0; -64,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-97,81; -67,92</t>
+          <t>-97,78; -64,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-92,21; -48,3</t>
+          <t>-93,24; -53,38</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -14,32</t>
+          <t>-19,08; -14,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -9,69</t>
+          <t>-14,42; -9,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -6,66</t>
+          <t>-11,2; -6,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -34,82</t>
+          <t>-43,64; -35,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -25,25</t>
+          <t>-35,28; -25,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -19,66</t>
+          <t>-30,72; -19,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 0,46</t>
+          <t>-12,28; -0,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 3,8</t>
+          <t>-8,42; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -1,75</t>
+          <t>-14,21; -1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 1,8</t>
+          <t>-27,09; 0,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 11,82</t>
+          <t>-20,95; 13,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,06; -5,03</t>
+          <t>-37,52; -4,86</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -11,17</t>
+          <t>-22,47; -10,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -4,31</t>
+          <t>-15,52; -3,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; -2,12</t>
+          <t>-13,31; -1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -21,8</t>
+          <t>-39,82; -21,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -9,27</t>
+          <t>-29,19; -8,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; -4,76</t>
+          <t>-27,83; -3,35</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -10,5</t>
+          <t>-21,37; -10,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -6,75</t>
+          <t>-17,97; -7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -1,39</t>
+          <t>-11,9; -1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,71; -20,59</t>
+          <t>-38,21; -20,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,51; -15,38</t>
+          <t>-35,89; -16,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,2; -3,49</t>
+          <t>-27,86; -3,29</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; -10,49</t>
+          <t>-23,32; -11,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -0,5</t>
+          <t>-12,46; -0,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -1,48</t>
+          <t>-12,87; -1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,62; -25,31</t>
+          <t>-48,01; -27,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,34; -1,15</t>
+          <t>-25,63; -0,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,46; -3,47</t>
+          <t>-28,15; -4,5</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,09; -15,64</t>
+          <t>-27,96; -15,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,73; -15,09</t>
+          <t>-27,33; -15,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -1,96</t>
+          <t>-14,26; -2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-74,38; -52,15</t>
+          <t>-75,96; -52,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,21; -45,5</t>
+          <t>-68,56; -45,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,71; -6,92</t>
+          <t>-41,58; -8,23</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -11,88</t>
+          <t>-21,15; -11,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -6,43</t>
+          <t>-16,57; -5,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -4,54</t>
+          <t>-15,19; -4,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-95,75; -77,03</t>
+          <t>-95,85; -78,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,89; -44,4</t>
+          <t>-82,49; -40,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; -30,84</t>
+          <t>-71,2; -30,58</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -5,32</t>
+          <t>-14,18; -5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -5,9</t>
+          <t>-14,97; -5,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -4,35</t>
+          <t>-11,73; -4,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -64,54</t>
+          <t>-96,77; -61,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-97,78; -64,98</t>
+          <t>-98,01; -67,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-93,24; -53,38</t>
+          <t>-92,48; -51,2</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -14,65</t>
+          <t>-18,96; -14,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -9,74</t>
+          <t>-14,4; -9,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -6,65</t>
+          <t>-11,33; -6,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -35,66</t>
+          <t>-43,67; -35,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -25,5</t>
+          <t>-35,29; -25,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -19,76</t>
+          <t>-31,15; -19,86</t>
         </is>
       </c>
     </row>
